--- a/resources/templates/standard/F1100-02.xlsx
+++ b/resources/templates/standard/F1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>교육 이수 보고서</t>
   </si>
@@ -648,11 +651,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -668,30 +673,30 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -768,7 +773,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -781,7 +786,7 @@
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -794,7 +799,7 @@
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
       <c r="W4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -809,7 +814,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -822,7 +827,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -835,7 +840,7 @@
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
@@ -850,7 +855,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -863,7 +868,7 @@
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -876,7 +881,7 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
       <c r="W6" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X6" s="15"/>
       <c r="Y6" s="15"/>
@@ -891,7 +896,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -963,7 +968,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -1665,12 +1670,12 @@
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1684,7 +1689,7 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
@@ -1776,12 +1781,12 @@
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
       <c r="D32" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -1795,7 +1800,7 @@
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
@@ -1804,13 +1809,13 @@
       <c r="U32" s="10"/>
       <c r="V32" s="10"/>
       <c r="W32" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X32" s="10"/>
       <c r="Y32" s="10"/>
       <c r="Z32" s="10"/>
       <c r="AA32" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
@@ -1824,7 +1829,7 @@
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
       <c r="D33" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -1861,7 +1866,7 @@
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -1875,7 +1880,7 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="22"/>
       <c r="R34" s="22"/>
@@ -1900,7 +1905,7 @@
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="D35" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
@@ -1914,7 +1919,7 @@
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q35" s="23"/>
       <c r="R35" s="23"/>
